--- a/FPO_Dashboard.xlsx
+++ b/FPO_Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPO_Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2F8677-7A0D-48D1-9FAE-09730BB681AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3A46E4-C499-4B38-8EC8-2A06E4953713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{08C0F3C2-BCA0-4DE6-8CAC-810E617DC01B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{08C0F3C2-BCA0-4DE6-8CAC-810E617DC01B}"/>
   </bookViews>
   <sheets>
     <sheet name="Mature" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1853" uniqueCount="819">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1996" uniqueCount="882">
   <si>
     <t>Indicators</t>
   </si>
@@ -2713,6 +2713,195 @@
   </si>
   <si>
     <t>No Procurement committee in place!</t>
+  </si>
+  <si>
+    <t>2026-04-16T08:16:40.173Z</t>
+  </si>
+  <si>
+    <t>Prakruthi Farmer Producers Mutually Aided Cooperative Society Ltd.</t>
+  </si>
+  <si>
+    <t>C. Prabhakar Reddy</t>
+  </si>
+  <si>
+    <t>Ayyavaripalle (V) &amp; (P), Vayalpadu Mandal, Annamayya District, AP, Pin : 517277</t>
+  </si>
+  <si>
+    <t>AMC/AYA/DCO/2024/08</t>
+  </si>
+  <si>
+    <t>district_cooperative_officer</t>
+  </si>
+  <si>
+    <t>1776237203359.pdf</t>
+  </si>
+  <si>
+    <t>1776237257030.pdf</t>
+  </si>
+  <si>
+    <t>1776250807522.pdf</t>
+  </si>
+  <si>
+    <t>1776327102632.pdf</t>
+  </si>
+  <si>
+    <t>Annamayya</t>
+  </si>
+  <si>
+    <t>Madanapalle Thamballapalle Valmikipuram</t>
+  </si>
+  <si>
+    <t>Bommanacheruvu Malepadu Eddulavaripalle Thamballapalle Ayyavaripalle Budidavedu Chintaparthi Chinthalavaripalle Nagarimadugu</t>
+  </si>
+  <si>
+    <t>1776327160504.pdf</t>
+  </si>
+  <si>
+    <t>1776251237408.pdf</t>
+  </si>
+  <si>
+    <t>1776251240226.pdf</t>
+  </si>
+  <si>
+    <t>1776250934660.pdf</t>
+  </si>
+  <si>
+    <t>paid_promoting_agency</t>
+  </si>
+  <si>
+    <t>marketing_person</t>
+  </si>
+  <si>
+    <t>pan gst amc_trade_licence</t>
+  </si>
+  <si>
+    <t>1776247944558.pdf</t>
+  </si>
+  <si>
+    <t>1776247977298.pdf</t>
+  </si>
+  <si>
+    <t>1776251355811.pdf</t>
+  </si>
+  <si>
+    <t>annual_financial_audit gst_filing</t>
+  </si>
+  <si>
+    <t>1776326815045.pdf</t>
+  </si>
+  <si>
+    <t>seed_sale tools_equipment_rental tools_equipment_sales farm_consumables bioinputs_sale animalfeed_sale other_inputs others</t>
+  </si>
+  <si>
+    <t>1776326745764.pdf</t>
+  </si>
+  <si>
+    <t>1776327358254.pdf</t>
+  </si>
+  <si>
+    <t>uuid:ac5142c0-7ac7-4ead-b318-8618334e717f</t>
+  </si>
+  <si>
+    <t>collect:KXeUl2I7JzTOEKe7</t>
+  </si>
+  <si>
+    <t>2026-04-11T13:12:18.391Z</t>
+  </si>
+  <si>
+    <t>JANAJEEVANA MACS</t>
+  </si>
+  <si>
+    <t>S Venkata Sivanna</t>
+  </si>
+  <si>
+    <t>G Uttappa</t>
+  </si>
+  <si>
+    <t>P.Kothapalli Village, Nallacheruvu Mandal, Sri Sathya Sai District.</t>
+  </si>
+  <si>
+    <t>AMC/ATP/DCO/2012/3844</t>
+  </si>
+  <si>
+    <t>1775786244549.pdf</t>
+  </si>
+  <si>
+    <t>1775788721890.pdf</t>
+  </si>
+  <si>
+    <t>1775788957047.jpg</t>
+  </si>
+  <si>
+    <t>1775801975439.xlsx</t>
+  </si>
+  <si>
+    <t>Sri_Sathya_Sai</t>
+  </si>
+  <si>
+    <t>Gandlapenta Nallacheruvu Talupula Nambulapulikunta Tanakal</t>
+  </si>
+  <si>
+    <t>G_Pedda_Thanda Gandlapenta Godduvelagala Katarupalli Kurumamidi Malameedapalli Somayajulapalli Veparala Allugundu Balepalli_Thanda Jogannapeta Kadiripulakunta Maddimadugu Nallacheruvu Oravoy P.Kothapalli Panthulacheruvu Talamarlavandlapalli Tavalamarri Ubbicherla Balija_Palli Dhaniyanicheruvu Tanakal Tavalam Mallireddipalli Kokkanti Talupula Pulligundlapalli Peddannavaripalli Gunduvaripalli Bandlapalli</t>
+  </si>
+  <si>
+    <t>1775789091884.pdf</t>
+  </si>
+  <si>
+    <t>accountant ceo procurement_coordinator marketing_person warehouse_charge processing_incharge</t>
+  </si>
+  <si>
+    <t>pan tan gst fssai amc_trade_licence professional_tax seed_licence nsc</t>
+  </si>
+  <si>
+    <t>1775789111332.jpg</t>
+  </si>
+  <si>
+    <t>1775789115289.jpg</t>
+  </si>
+  <si>
+    <t>1775789120805.pdf</t>
+  </si>
+  <si>
+    <t>1775789231240.pdf</t>
+  </si>
+  <si>
+    <t>1775789239742.pdf</t>
+  </si>
+  <si>
+    <t>1775802291085.pdf</t>
+  </si>
+  <si>
+    <t>1775802269290.pdf</t>
+  </si>
+  <si>
+    <t>warehouse_godown destoner grader dehuller_mill oil_expeller pulveriser packing_machine moisture_meters grading_tables pallets_crates sewing_machine commercial_vehicle office_furniture laptops others</t>
+  </si>
+  <si>
+    <t>1775802425917.jpg</t>
+  </si>
+  <si>
+    <t>1775789445659.pdf</t>
+  </si>
+  <si>
+    <t>1775789409862.pdf</t>
+  </si>
+  <si>
+    <t>seed_sale tools_equipment_rental tools_equipment_sales bioinputs_sale animalfeed_sale other_inputs food_crops fresh_products high_value_crops value_added onward_lending others</t>
+  </si>
+  <si>
+    <t>1775804341197.pdf</t>
+  </si>
+  <si>
+    <t>1775804540796.pdf</t>
+  </si>
+  <si>
+    <t>1775804673809.xls</t>
+  </si>
+  <si>
+    <t>uuid:b3607d03-335a-45a3-ac61-0d5e2329a350</t>
+  </si>
+  <si>
+    <t>collect:vgehtewNzO5PLZVA</t>
   </si>
 </sst>
 </file>
@@ -4192,16 +4381,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89410E0D-D0ED-4CEA-A634-03BBE3F1C57D}">
-  <dimension ref="A1:ES4"/>
+  <dimension ref="A1:ES6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="58.26953125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27.6328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="68" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.6328125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="43.26953125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="34.7265625" bestFit="1" customWidth="1"/>
@@ -4241,10 +4430,10 @@
     <col min="44" max="44" width="43.453125" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="32.453125" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="30.54296875" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="51.90625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="54.26953125" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="33.08984375" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="31.1796875" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="84.90625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="255.6328125" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="27.90625" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="26" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="32" bestFit="1" customWidth="1"/>
@@ -4283,7 +4472,7 @@
     <col min="86" max="86" width="31.08984375" bestFit="1" customWidth="1"/>
     <col min="87" max="87" width="24.08984375" bestFit="1" customWidth="1"/>
     <col min="88" max="88" width="37.81640625" bestFit="1" customWidth="1"/>
-    <col min="89" max="89" width="52.1796875" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="86.6328125" bestFit="1" customWidth="1"/>
     <col min="90" max="90" width="35.54296875" bestFit="1" customWidth="1"/>
     <col min="91" max="91" width="49.26953125" bestFit="1" customWidth="1"/>
     <col min="92" max="92" width="44.54296875" bestFit="1" customWidth="1"/>
@@ -4301,7 +4490,7 @@
     <col min="104" max="104" width="49.90625" bestFit="1" customWidth="1"/>
     <col min="105" max="105" width="57.26953125" bestFit="1" customWidth="1"/>
     <col min="106" max="106" width="32.81640625" bestFit="1" customWidth="1"/>
-    <col min="107" max="107" width="131" bestFit="1" customWidth="1"/>
+    <col min="107" max="107" width="176.7265625" bestFit="1" customWidth="1"/>
     <col min="108" max="108" width="56.1796875" bestFit="1" customWidth="1"/>
     <col min="109" max="109" width="54.90625" bestFit="1" customWidth="1"/>
     <col min="110" max="110" width="49.7265625" bestFit="1" customWidth="1"/>
@@ -4324,7 +4513,7 @@
     <col min="127" max="127" width="78.1796875" bestFit="1" customWidth="1"/>
     <col min="128" max="128" width="39" bestFit="1" customWidth="1"/>
     <col min="129" max="129" width="47.08984375" bestFit="1" customWidth="1"/>
-    <col min="130" max="130" width="134.26953125" bestFit="1" customWidth="1"/>
+    <col min="130" max="130" width="159.36328125" bestFit="1" customWidth="1"/>
     <col min="131" max="131" width="36.7265625" bestFit="1" customWidth="1"/>
     <col min="132" max="132" width="87.36328125" bestFit="1" customWidth="1"/>
     <col min="133" max="133" width="36.36328125" bestFit="1" customWidth="1"/>
@@ -4796,34 +4985,31 @@
     </row>
     <row r="2" spans="1:149" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>318</v>
+        <v>819</v>
       </c>
       <c r="C2" t="s">
         <v>317</v>
       </c>
       <c r="D2" t="s">
-        <v>319</v>
+        <v>820</v>
       </c>
       <c r="E2" t="s">
-        <v>320</v>
-      </c>
-      <c r="F2" t="s">
-        <v>321</v>
+        <v>821</v>
       </c>
       <c r="G2" t="s">
-        <v>322</v>
+        <v>822</v>
       </c>
       <c r="H2">
-        <v>3000000</v>
+        <v>512000</v>
       </c>
       <c r="I2" t="s">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="K2" s="19">
-        <v>42736</v>
+        <v>45292</v>
       </c>
       <c r="L2" t="s">
-        <v>323</v>
+        <v>823</v>
       </c>
       <c r="M2" t="s">
         <v>317</v>
@@ -4832,7 +5018,7 @@
         <v>317</v>
       </c>
       <c r="O2" t="s">
-        <v>181</v>
+        <v>824</v>
       </c>
       <c r="P2" t="s">
         <v>317</v>
@@ -4846,44 +5032,50 @@
       <c r="S2" t="s">
         <v>317</v>
       </c>
-      <c r="T2">
-        <v>2498000</v>
+      <c r="U2" t="s">
+        <v>825</v>
+      </c>
+      <c r="V2" t="s">
+        <v>826</v>
+      </c>
+      <c r="W2" t="s">
+        <v>827</v>
       </c>
       <c r="X2">
-        <v>1507</v>
+        <v>512</v>
       </c>
       <c r="Y2">
-        <v>700</v>
+        <v>352</v>
       </c>
       <c r="Z2">
-        <v>807</v>
+        <v>160</v>
       </c>
       <c r="AA2">
-        <v>1507</v>
+        <v>512</v>
       </c>
       <c r="AB2">
         <v>1000</v>
       </c>
       <c r="AC2">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="AD2">
-        <v>2498000</v>
+        <v>2</v>
       </c>
       <c r="AE2">
-        <v>1507</v>
+        <v>74</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>412</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AH2">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AI2">
-        <v>1450</v>
+        <v>258</v>
       </c>
       <c r="AJ2" t="s">
         <v>317</v>
@@ -4903,35 +5095,50 @@
       <c r="AO2" t="s">
         <v>317</v>
       </c>
+      <c r="AP2" t="s">
+        <v>828</v>
+      </c>
       <c r="AQ2" t="s">
         <v>186</v>
       </c>
       <c r="AR2" t="s">
-        <v>325</v>
+        <v>829</v>
       </c>
       <c r="AS2">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>830</v>
+      </c>
+      <c r="AV2">
         <v>3</v>
       </c>
-      <c r="AU2" t="s">
-        <v>326</v>
-      </c>
-      <c r="AV2">
-        <v>5</v>
+      <c r="AX2" t="s">
+        <v>831</v>
       </c>
       <c r="AY2">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="BA2">
+        <v>59</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>832</v>
       </c>
       <c r="BC2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BE2">
         <v>5</v>
       </c>
       <c r="BF2">
-        <v>102</v>
+        <v>3</v>
+      </c>
+      <c r="BG2">
+        <v>2</v>
       </c>
       <c r="BH2" t="s">
         <v>317</v>
@@ -4951,11 +5158,17 @@
       <c r="BM2" t="s">
         <v>317</v>
       </c>
+      <c r="BN2" t="s">
+        <v>833</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>834</v>
+      </c>
       <c r="BP2" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="BQ2">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="BR2" t="s">
         <v>193</v>
@@ -4976,79 +5189,91 @@
         <v>317</v>
       </c>
       <c r="BX2">
-        <v>350</v>
+        <v>1</v>
       </c>
       <c r="BY2" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="CA2" t="s">
         <v>317</v>
       </c>
       <c r="CB2" s="19">
-        <v>45930</v>
+        <v>45989</v>
       </c>
       <c r="CC2">
-        <v>820</v>
+        <v>262</v>
       </c>
       <c r="CD2" t="s">
-        <v>317</v>
-      </c>
-      <c r="CE2">
-        <v>250000</v>
+        <v>324</v>
       </c>
       <c r="CF2" t="s">
         <v>317</v>
       </c>
+      <c r="CG2" t="s">
+        <v>835</v>
+      </c>
       <c r="CH2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CI2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CJ2" t="s">
-        <v>196</v>
+        <v>836</v>
       </c>
       <c r="CK2" t="s">
-        <v>327</v>
+        <v>837</v>
       </c>
       <c r="CL2" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="CM2" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="CP2" t="s">
-        <v>328</v>
+        <v>838</v>
+      </c>
+      <c r="CQ2" t="s">
+        <v>839</v>
+      </c>
+      <c r="CS2" t="s">
+        <v>840</v>
+      </c>
+      <c r="CV2" t="s">
+        <v>841</v>
       </c>
       <c r="DB2" t="s">
-        <v>317</v>
-      </c>
-      <c r="DC2" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="DS2" t="s">
-        <v>330</v>
+        <v>842</v>
+      </c>
+      <c r="DT2" t="s">
+        <v>843</v>
       </c>
       <c r="DX2">
-        <v>150</v>
+        <v>420</v>
       </c>
       <c r="DY2">
-        <v>25000</v>
+        <v>3000</v>
       </c>
       <c r="DZ2" t="s">
-        <v>331</v>
+        <v>844</v>
+      </c>
+      <c r="EA2" t="s">
+        <v>845</v>
       </c>
       <c r="EB2" t="s">
-        <v>332</v>
-      </c>
-      <c r="EF2" t="s">
-        <v>333</v>
+        <v>233</v>
+      </c>
+      <c r="EC2" t="s">
+        <v>846</v>
       </c>
       <c r="EI2" t="s">
-        <v>334</v>
+        <v>847</v>
       </c>
       <c r="EJ2" t="s">
-        <v>334</v>
+        <v>847</v>
       </c>
       <c r="EK2">
         <v>279</v>
@@ -5057,13 +5282,13 @@
         <v>211</v>
       </c>
       <c r="EM2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="EN2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="EQ2" t="s">
-        <v>335</v>
+        <v>848</v>
       </c>
       <c r="ER2">
         <v>0</v>
@@ -5074,34 +5299,34 @@
     </row>
     <row r="3" spans="1:149" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>174</v>
+        <v>849</v>
       </c>
       <c r="C3" t="s">
         <v>317</v>
       </c>
       <c r="D3" t="s">
-        <v>175</v>
+        <v>850</v>
       </c>
       <c r="E3" t="s">
-        <v>176</v>
+        <v>851</v>
       </c>
       <c r="F3" t="s">
-        <v>177</v>
+        <v>852</v>
       </c>
       <c r="G3" t="s">
-        <v>178</v>
+        <v>853</v>
       </c>
       <c r="H3">
-        <v>500000</v>
+        <v>5</v>
       </c>
       <c r="I3" t="s">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="K3" s="19">
-        <v>45292</v>
+        <v>40909</v>
       </c>
       <c r="L3" t="s">
-        <v>180</v>
+        <v>854</v>
       </c>
       <c r="M3" t="s">
         <v>317</v>
@@ -5110,7 +5335,7 @@
         <v>317</v>
       </c>
       <c r="O3" t="s">
-        <v>181</v>
+        <v>824</v>
       </c>
       <c r="P3" t="s">
         <v>317</v>
@@ -5124,53 +5349,50 @@
       <c r="S3" t="s">
         <v>317</v>
       </c>
-      <c r="T3" t="s">
-        <v>23</v>
-      </c>
       <c r="U3" t="s">
-        <v>182</v>
+        <v>855</v>
       </c>
       <c r="V3" t="s">
-        <v>183</v>
+        <v>856</v>
       </c>
       <c r="W3" t="s">
-        <v>184</v>
+        <v>857</v>
       </c>
       <c r="X3">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="Y3">
-        <v>328</v>
+        <v>434</v>
       </c>
       <c r="Z3">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="AA3">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AB3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AC3">
         <v>1000</v>
       </c>
       <c r="AD3">
-        <v>10000</v>
+        <v>506110</v>
       </c>
       <c r="AE3">
-        <v>320</v>
+        <v>504</v>
       </c>
       <c r="AF3">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="AG3">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="AI3">
-        <v>3456</v>
+        <v>350</v>
       </c>
       <c r="AJ3" t="s">
         <v>317</v>
@@ -5191,46 +5413,46 @@
         <v>317</v>
       </c>
       <c r="AP3" t="s">
-        <v>185</v>
+        <v>858</v>
       </c>
       <c r="AQ3" t="s">
         <v>186</v>
       </c>
       <c r="AR3" t="s">
-        <v>187</v>
+        <v>859</v>
       </c>
       <c r="AS3">
         <v>1</v>
       </c>
       <c r="AU3" t="s">
-        <v>188</v>
+        <v>860</v>
       </c>
       <c r="AV3">
         <v>5</v>
       </c>
       <c r="AX3" t="s">
-        <v>189</v>
+        <v>861</v>
       </c>
       <c r="AY3">
+        <v>31</v>
+      </c>
+      <c r="BA3">
+        <v>75</v>
+      </c>
+      <c r="BC3">
         <v>11</v>
       </c>
-      <c r="BA3">
-        <v>65</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>190</v>
-      </c>
-      <c r="BC3">
-        <v>10</v>
-      </c>
       <c r="BD3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BE3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF3">
-        <v>100</v>
+        <v>3</v>
+      </c>
+      <c r="BG3">
+        <v>11</v>
       </c>
       <c r="BH3" t="s">
         <v>317</v>
@@ -5250,17 +5472,11 @@
       <c r="BM3" t="s">
         <v>317</v>
       </c>
-      <c r="BN3" t="s">
-        <v>191</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>192</v>
-      </c>
       <c r="BP3" t="s">
         <v>317</v>
       </c>
       <c r="BQ3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BR3" t="s">
         <v>193</v>
@@ -5286,17 +5502,14 @@
       <c r="BY3" t="s">
         <v>317</v>
       </c>
-      <c r="BZ3" t="s">
-        <v>194</v>
-      </c>
       <c r="CA3" t="s">
         <v>317</v>
       </c>
       <c r="CB3" s="19">
-        <v>46136</v>
+        <v>46065</v>
       </c>
       <c r="CC3">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="CD3" t="s">
         <v>324</v>
@@ -5305,76 +5518,97 @@
         <v>317</v>
       </c>
       <c r="CG3" t="s">
-        <v>195</v>
+        <v>862</v>
       </c>
       <c r="CH3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="CI3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ3" t="s">
-        <v>196</v>
+        <v>836</v>
       </c>
       <c r="CK3" t="s">
-        <v>197</v>
+        <v>863</v>
       </c>
       <c r="CL3" t="s">
         <v>317</v>
       </c>
       <c r="CM3" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="CP3" t="s">
-        <v>198</v>
+        <v>864</v>
       </c>
       <c r="CQ3" t="s">
-        <v>199</v>
+        <v>865</v>
       </c>
       <c r="CR3" t="s">
-        <v>200</v>
+        <v>866</v>
       </c>
       <c r="CS3" t="s">
-        <v>201</v>
+        <v>867</v>
+      </c>
+      <c r="CT3" t="s">
+        <v>868</v>
+      </c>
+      <c r="CV3" t="s">
+        <v>869</v>
+      </c>
+      <c r="CX3" t="s">
+        <v>870</v>
+      </c>
+      <c r="CY3" t="s">
+        <v>871</v>
       </c>
       <c r="DB3" t="s">
         <v>317</v>
       </c>
       <c r="DC3" t="s">
-        <v>202</v>
+        <v>872</v>
+      </c>
+      <c r="DE3" t="s">
+        <v>873</v>
       </c>
       <c r="DS3" t="s">
-        <v>203</v>
+        <v>330</v>
       </c>
       <c r="DT3" t="s">
-        <v>204</v>
+        <v>874</v>
       </c>
       <c r="DU3" t="s">
-        <v>205</v>
+        <v>875</v>
       </c>
       <c r="DX3">
-        <v>45</v>
+        <v>780</v>
       </c>
       <c r="DY3">
-        <v>25000</v>
+        <v>5000</v>
       </c>
       <c r="DZ3" t="s">
-        <v>206</v>
+        <v>876</v>
+      </c>
+      <c r="EA3" t="s">
+        <v>877</v>
       </c>
       <c r="EB3" t="s">
-        <v>207</v>
+        <v>332</v>
       </c>
       <c r="EC3" t="s">
-        <v>208</v>
+        <v>878</v>
       </c>
       <c r="EF3" t="s">
-        <v>209</v>
+        <v>333</v>
+      </c>
+      <c r="EG3" t="s">
+        <v>879</v>
       </c>
       <c r="EI3" t="s">
-        <v>210</v>
+        <v>880</v>
       </c>
       <c r="EJ3" t="s">
-        <v>210</v>
+        <v>880</v>
       </c>
       <c r="EK3">
         <v>279</v>
@@ -5383,13 +5617,13 @@
         <v>211</v>
       </c>
       <c r="EM3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="EN3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="EQ3" t="s">
-        <v>212</v>
+        <v>881</v>
       </c>
       <c r="ER3">
         <v>0</v>
@@ -5400,31 +5634,34 @@
     </row>
     <row r="4" spans="1:149" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>214</v>
+        <v>318</v>
       </c>
       <c r="C4" t="s">
         <v>317</v>
       </c>
       <c r="D4" t="s">
-        <v>215</v>
+        <v>319</v>
       </c>
       <c r="E4" t="s">
-        <v>216</v>
+        <v>320</v>
       </c>
       <c r="F4" t="s">
-        <v>217</v>
+        <v>321</v>
       </c>
       <c r="G4" t="s">
-        <v>215</v>
+        <v>322</v>
+      </c>
+      <c r="H4">
+        <v>3000000</v>
       </c>
       <c r="I4" t="s">
-        <v>218</v>
+        <v>179</v>
       </c>
       <c r="K4" s="19">
         <v>42736</v>
       </c>
       <c r="L4" t="s">
-        <v>219</v>
+        <v>323</v>
       </c>
       <c r="M4" t="s">
         <v>317</v>
@@ -5433,55 +5670,58 @@
         <v>317</v>
       </c>
       <c r="O4" t="s">
-        <v>220</v>
+        <v>181</v>
       </c>
       <c r="P4" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q4" s="19">
+        <v>45658</v>
+      </c>
+      <c r="R4" t="s">
         <v>324</v>
-      </c>
-      <c r="Q4" s="19">
-        <v>44562</v>
-      </c>
-      <c r="R4" t="s">
-        <v>317</v>
       </c>
       <c r="S4" t="s">
         <v>317</v>
       </c>
       <c r="T4">
-        <v>500000</v>
-      </c>
-      <c r="U4" t="s">
-        <v>221</v>
-      </c>
-      <c r="V4" t="s">
-        <v>222</v>
-      </c>
-      <c r="W4" t="s">
-        <v>223</v>
+        <v>2498000</v>
       </c>
       <c r="X4">
-        <v>512</v>
+        <v>1507</v>
       </c>
       <c r="Y4">
-        <v>1</v>
+        <v>700</v>
       </c>
       <c r="Z4">
-        <v>511</v>
+        <v>807</v>
       </c>
       <c r="AA4">
-        <v>512</v>
+        <v>1507</v>
       </c>
       <c r="AB4">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="AD4">
-        <v>500000</v>
+        <v>2498000</v>
+      </c>
+      <c r="AE4">
+        <v>1507</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>120</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1450</v>
       </c>
       <c r="AJ4" t="s">
         <v>317</v>
@@ -5490,13 +5730,13 @@
         <v>317</v>
       </c>
       <c r="AL4" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="AM4" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="AN4" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="AO4" t="s">
         <v>317</v>
@@ -5505,37 +5745,37 @@
         <v>186</v>
       </c>
       <c r="AR4" t="s">
-        <v>187</v>
+        <v>325</v>
       </c>
       <c r="AS4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU4" t="s">
-        <v>224</v>
+        <v>326</v>
       </c>
       <c r="AV4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AY4">
         <v>0</v>
       </c>
-      <c r="BA4">
-        <v>55</v>
-      </c>
       <c r="BC4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD4">
         <v>10</v>
       </c>
       <c r="BE4">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="BF4">
+        <v>102</v>
       </c>
       <c r="BH4" t="s">
         <v>317</v>
       </c>
       <c r="BI4" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="BJ4" t="s">
         <v>317</v>
@@ -5547,19 +5787,19 @@
         <v>317</v>
       </c>
       <c r="BM4" t="s">
+        <v>317</v>
+      </c>
+      <c r="BP4" t="s">
         <v>324</v>
       </c>
-      <c r="BN4" t="s">
-        <v>225</v>
-      </c>
-      <c r="BP4" t="s">
-        <v>317</v>
+      <c r="BQ4">
+        <v>72</v>
       </c>
       <c r="BR4" t="s">
         <v>193</v>
       </c>
       <c r="BS4" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="BT4" t="s">
         <v>317</v>
@@ -5567,71 +5807,86 @@
       <c r="BU4" t="s">
         <v>317</v>
       </c>
+      <c r="BV4" t="s">
+        <v>317</v>
+      </c>
+      <c r="BW4" t="s">
+        <v>317</v>
+      </c>
+      <c r="BX4">
+        <v>350</v>
+      </c>
+      <c r="BY4" t="s">
+        <v>317</v>
+      </c>
+      <c r="CA4" t="s">
+        <v>317</v>
+      </c>
+      <c r="CB4" s="19">
+        <v>45930</v>
+      </c>
+      <c r="CC4">
+        <v>820</v>
+      </c>
       <c r="CD4" t="s">
-        <v>324</v>
+        <v>317</v>
+      </c>
+      <c r="CE4">
+        <v>250000</v>
       </c>
       <c r="CF4" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="CH4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="CI4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="CJ4" t="s">
         <v>196</v>
       </c>
       <c r="CK4" t="s">
-        <v>197</v>
+        <v>327</v>
       </c>
       <c r="CL4" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="CM4" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="CP4" t="s">
-        <v>226</v>
-      </c>
-      <c r="CQ4" t="s">
-        <v>227</v>
-      </c>
-      <c r="CS4" t="s">
-        <v>228</v>
+        <v>328</v>
       </c>
       <c r="DB4" t="s">
-        <v>324</v>
+        <v>317</v>
+      </c>
+      <c r="DC4" t="s">
+        <v>329</v>
       </c>
       <c r="DS4" t="s">
-        <v>229</v>
-      </c>
-      <c r="DT4" t="s">
-        <v>230</v>
-      </c>
-      <c r="DU4" t="s">
-        <v>231</v>
+        <v>330</v>
       </c>
       <c r="DX4">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="DY4">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="DZ4" t="s">
-        <v>232</v>
+        <v>331</v>
       </c>
       <c r="EB4" t="s">
-        <v>233</v>
+        <v>332</v>
       </c>
       <c r="EF4" t="s">
-        <v>234</v>
+        <v>333</v>
       </c>
       <c r="EI4" t="s">
-        <v>235</v>
+        <v>334</v>
       </c>
       <c r="EJ4" t="s">
-        <v>235</v>
+        <v>334</v>
       </c>
       <c r="EK4">
         <v>279</v>
@@ -5640,18 +5895,601 @@
         <v>211</v>
       </c>
       <c r="EM4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="EN4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="EQ4" t="s">
-        <v>236</v>
+        <v>335</v>
       </c>
       <c r="ER4">
         <v>0</v>
       </c>
       <c r="ES4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:149" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C5" t="s">
+        <v>317</v>
+      </c>
+      <c r="D5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F5" t="s">
+        <v>177</v>
+      </c>
+      <c r="G5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H5">
+        <v>500000</v>
+      </c>
+      <c r="I5" t="s">
+        <v>179</v>
+      </c>
+      <c r="K5" s="19">
+        <v>45292</v>
+      </c>
+      <c r="L5" t="s">
+        <v>180</v>
+      </c>
+      <c r="M5" t="s">
+        <v>317</v>
+      </c>
+      <c r="N5" t="s">
+        <v>317</v>
+      </c>
+      <c r="O5" t="s">
+        <v>181</v>
+      </c>
+      <c r="P5" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q5" s="19">
+        <v>45658</v>
+      </c>
+      <c r="R5" t="s">
+        <v>324</v>
+      </c>
+      <c r="S5" t="s">
+        <v>317</v>
+      </c>
+      <c r="T5" t="s">
+        <v>23</v>
+      </c>
+      <c r="U5" t="s">
+        <v>182</v>
+      </c>
+      <c r="V5" t="s">
+        <v>183</v>
+      </c>
+      <c r="W5" t="s">
+        <v>184</v>
+      </c>
+      <c r="X5">
+        <v>518</v>
+      </c>
+      <c r="Y5">
+        <v>328</v>
+      </c>
+      <c r="Z5">
+        <v>190</v>
+      </c>
+      <c r="AA5">
+        <v>518</v>
+      </c>
+      <c r="AB5">
+        <v>100</v>
+      </c>
+      <c r="AC5">
+        <v>1000</v>
+      </c>
+      <c r="AD5">
+        <v>10000</v>
+      </c>
+      <c r="AE5">
+        <v>320</v>
+      </c>
+      <c r="AF5">
+        <v>120</v>
+      </c>
+      <c r="AG5">
+        <v>65</v>
+      </c>
+      <c r="AH5">
+        <v>13</v>
+      </c>
+      <c r="AI5">
+        <v>3456</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>317</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>317</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>317</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>317</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>317</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>317</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>185</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>186</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>187</v>
+      </c>
+      <c r="AS5">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>188</v>
+      </c>
+      <c r="AV5">
+        <v>5</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>189</v>
+      </c>
+      <c r="AY5">
+        <v>11</v>
+      </c>
+      <c r="BA5">
+        <v>65</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>190</v>
+      </c>
+      <c r="BC5">
+        <v>10</v>
+      </c>
+      <c r="BD5">
+        <v>10</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>100</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>317</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>317</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>317</v>
+      </c>
+      <c r="BK5" t="s">
+        <v>317</v>
+      </c>
+      <c r="BL5" t="s">
+        <v>317</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>317</v>
+      </c>
+      <c r="BN5" t="s">
+        <v>191</v>
+      </c>
+      <c r="BO5" t="s">
+        <v>192</v>
+      </c>
+      <c r="BP5" t="s">
+        <v>317</v>
+      </c>
+      <c r="BQ5">
+        <v>28</v>
+      </c>
+      <c r="BR5" t="s">
+        <v>193</v>
+      </c>
+      <c r="BS5" t="s">
+        <v>317</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>317</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>317</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>317</v>
+      </c>
+      <c r="BW5" t="s">
+        <v>317</v>
+      </c>
+      <c r="BX5">
+        <v>2</v>
+      </c>
+      <c r="BY5" t="s">
+        <v>317</v>
+      </c>
+      <c r="BZ5" t="s">
+        <v>194</v>
+      </c>
+      <c r="CA5" t="s">
+        <v>317</v>
+      </c>
+      <c r="CB5" s="19">
+        <v>46136</v>
+      </c>
+      <c r="CC5">
+        <v>150</v>
+      </c>
+      <c r="CD5" t="s">
+        <v>324</v>
+      </c>
+      <c r="CF5" t="s">
+        <v>317</v>
+      </c>
+      <c r="CG5" t="s">
+        <v>195</v>
+      </c>
+      <c r="CH5">
+        <v>1</v>
+      </c>
+      <c r="CI5">
+        <v>1</v>
+      </c>
+      <c r="CJ5" t="s">
+        <v>196</v>
+      </c>
+      <c r="CK5" t="s">
+        <v>197</v>
+      </c>
+      <c r="CL5" t="s">
+        <v>317</v>
+      </c>
+      <c r="CM5" t="s">
+        <v>317</v>
+      </c>
+      <c r="CP5" t="s">
+        <v>198</v>
+      </c>
+      <c r="CQ5" t="s">
+        <v>199</v>
+      </c>
+      <c r="CR5" t="s">
+        <v>200</v>
+      </c>
+      <c r="CS5" t="s">
+        <v>201</v>
+      </c>
+      <c r="DB5" t="s">
+        <v>317</v>
+      </c>
+      <c r="DC5" t="s">
+        <v>202</v>
+      </c>
+      <c r="DS5" t="s">
+        <v>203</v>
+      </c>
+      <c r="DT5" t="s">
+        <v>204</v>
+      </c>
+      <c r="DU5" t="s">
+        <v>205</v>
+      </c>
+      <c r="DX5">
+        <v>45</v>
+      </c>
+      <c r="DY5">
+        <v>25000</v>
+      </c>
+      <c r="DZ5" t="s">
+        <v>206</v>
+      </c>
+      <c r="EB5" t="s">
+        <v>207</v>
+      </c>
+      <c r="EC5" t="s">
+        <v>208</v>
+      </c>
+      <c r="EF5" t="s">
+        <v>209</v>
+      </c>
+      <c r="EI5" t="s">
+        <v>210</v>
+      </c>
+      <c r="EJ5" t="s">
+        <v>210</v>
+      </c>
+      <c r="EK5">
+        <v>279</v>
+      </c>
+      <c r="EL5" t="s">
+        <v>211</v>
+      </c>
+      <c r="EM5">
+        <v>15</v>
+      </c>
+      <c r="EN5">
+        <v>15</v>
+      </c>
+      <c r="EQ5" t="s">
+        <v>212</v>
+      </c>
+      <c r="ER5">
+        <v>0</v>
+      </c>
+      <c r="ES5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:149" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>214</v>
+      </c>
+      <c r="C6" t="s">
+        <v>317</v>
+      </c>
+      <c r="D6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E6" t="s">
+        <v>216</v>
+      </c>
+      <c r="F6" t="s">
+        <v>217</v>
+      </c>
+      <c r="G6" t="s">
+        <v>215</v>
+      </c>
+      <c r="I6" t="s">
+        <v>218</v>
+      </c>
+      <c r="K6" s="19">
+        <v>42736</v>
+      </c>
+      <c r="L6" t="s">
+        <v>219</v>
+      </c>
+      <c r="M6" t="s">
+        <v>317</v>
+      </c>
+      <c r="N6" t="s">
+        <v>317</v>
+      </c>
+      <c r="O6" t="s">
+        <v>220</v>
+      </c>
+      <c r="P6" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q6" s="19">
+        <v>44562</v>
+      </c>
+      <c r="R6" t="s">
+        <v>317</v>
+      </c>
+      <c r="S6" t="s">
+        <v>317</v>
+      </c>
+      <c r="T6">
+        <v>500000</v>
+      </c>
+      <c r="U6" t="s">
+        <v>221</v>
+      </c>
+      <c r="V6" t="s">
+        <v>222</v>
+      </c>
+      <c r="W6" t="s">
+        <v>223</v>
+      </c>
+      <c r="X6">
+        <v>512</v>
+      </c>
+      <c r="Y6">
+        <v>1</v>
+      </c>
+      <c r="Z6">
+        <v>511</v>
+      </c>
+      <c r="AA6">
+        <v>512</v>
+      </c>
+      <c r="AB6">
+        <v>100</v>
+      </c>
+      <c r="AC6">
+        <v>500</v>
+      </c>
+      <c r="AD6">
+        <v>500000</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>317</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>317</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>324</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>324</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>324</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>317</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>186</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>187</v>
+      </c>
+      <c r="AS6">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>224</v>
+      </c>
+      <c r="AV6">
+        <v>1</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>55</v>
+      </c>
+      <c r="BC6">
+        <v>11</v>
+      </c>
+      <c r="BD6">
+        <v>10</v>
+      </c>
+      <c r="BE6">
+        <v>1</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>317</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>324</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>317</v>
+      </c>
+      <c r="BK6" t="s">
+        <v>317</v>
+      </c>
+      <c r="BL6" t="s">
+        <v>317</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>324</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>225</v>
+      </c>
+      <c r="BP6" t="s">
+        <v>317</v>
+      </c>
+      <c r="BR6" t="s">
+        <v>193</v>
+      </c>
+      <c r="BS6" t="s">
+        <v>324</v>
+      </c>
+      <c r="BT6" t="s">
+        <v>317</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>317</v>
+      </c>
+      <c r="CD6" t="s">
+        <v>324</v>
+      </c>
+      <c r="CF6" t="s">
+        <v>324</v>
+      </c>
+      <c r="CH6">
+        <v>1</v>
+      </c>
+      <c r="CI6">
+        <v>1</v>
+      </c>
+      <c r="CJ6" t="s">
+        <v>196</v>
+      </c>
+      <c r="CK6" t="s">
+        <v>197</v>
+      </c>
+      <c r="CL6" t="s">
+        <v>324</v>
+      </c>
+      <c r="CM6" t="s">
+        <v>324</v>
+      </c>
+      <c r="CP6" t="s">
+        <v>226</v>
+      </c>
+      <c r="CQ6" t="s">
+        <v>227</v>
+      </c>
+      <c r="CS6" t="s">
+        <v>228</v>
+      </c>
+      <c r="DB6" t="s">
+        <v>324</v>
+      </c>
+      <c r="DS6" t="s">
+        <v>229</v>
+      </c>
+      <c r="DT6" t="s">
+        <v>230</v>
+      </c>
+      <c r="DU6" t="s">
+        <v>231</v>
+      </c>
+      <c r="DX6">
+        <v>0</v>
+      </c>
+      <c r="DY6">
+        <v>0</v>
+      </c>
+      <c r="DZ6" t="s">
+        <v>232</v>
+      </c>
+      <c r="EB6" t="s">
+        <v>233</v>
+      </c>
+      <c r="EF6" t="s">
+        <v>234</v>
+      </c>
+      <c r="EI6" t="s">
+        <v>235</v>
+      </c>
+      <c r="EJ6" t="s">
+        <v>235</v>
+      </c>
+      <c r="EK6">
+        <v>279</v>
+      </c>
+      <c r="EL6" t="s">
+        <v>211</v>
+      </c>
+      <c r="EM6">
+        <v>8</v>
+      </c>
+      <c r="EN6">
+        <v>8</v>
+      </c>
+      <c r="EQ6" t="s">
+        <v>236</v>
+      </c>
+      <c r="ER6">
+        <v>0</v>
+      </c>
+      <c r="ES6" t="s">
         <v>237</v>
       </c>
     </row>
